--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -658,11 +658,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2030,7 +2025,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>5581999999999</t>
+          <t>5581999180003</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -2077,7 +2072,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Paulista – PE</t>
+          <t>Avenida B, nº 5, Loja C – Maranguape II, Paulista – PE, CEP 53421-036</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -1,59 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Produtos" sheetId="1" r:id="rId1"/>
-    <sheet name="Configurações" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como usar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configurações" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="7">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001747D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,19 +83,167 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DCE3EF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DCE3EF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCE3EF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCE3EF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>POP BRILHO</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Sim = aparece na loja. Não = esconde (sem apagar).</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Nome do produto como aparece na loja. Obrigatório.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Agrupa os produtos nos filtros da loja.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Volume, peso ou quantidade. Ex.: 500 ml, 2 L, 4 unidades.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Preço de venda. Obrigatório.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Aparece riscado ao lado do preço.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Etiqueta no canto da foto. Ex.: Oferta, Novo.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Nome exato do arquivo enviado para a pasta fotos no GitHub. Ex.: detergente-neutro.jpg</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -151,7 +321,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -186,7 +355,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -221,16 +389,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,164 +524,1564 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col width="130" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Ativo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Categoria</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Tamanho</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Preço</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Preço antigo</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Selo</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Foto</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COMO EDITAR A LOJA POP BRILHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. Esta planilha controla os produtos e os dados da loja no site. Edite aqui, salve e envie para o GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. Para ADICIONAR um produto: preencha uma nova linha na aba Produtos (Nome e Preço são obrigatórios).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3. Para EDITAR: altere o texto ou o preço direto na linha do produto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>4. Para TIRAR um produto da loja: mude Ativo para Não (ou apague a linha).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5. A ordem das linhas é a ordem em que os produtos aparecem na loja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6. Categorias novas aparecem sozinhas nos filtros da loja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>FOTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>7. Tire a foto do produto (de preferência com fundo branco, quadrada) e dê um nome simples ao arquivo, sem espaços. Ex.: agua-sanitaria.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>8. No computador, crie uma pasta chamada fotos e coloque as fotos dentro. No GitHub (repositório popbrilho-dados): Add file → Upload files → arraste a PASTA fotos inteira → Commit changes. Para fotos novas depois, entre na pasta fotos no GitHub e use Add file → Upload files lá dentro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>9. Na coluna Foto, escreva exatamente o nome do arquivo (ex.: agua-sanitaria.jpg). Sem foto, a loja mostra um desenho do produto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>PUBLICAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>10. Salve esta planilha com o nome produtos.xlsx (mesmo nome sempre).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>11. No GitHub: Add file → Upload files → arraste produtos.xlsx → Commit changes. Em 1 a 2 minutos o site atualiza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Células com fundo amarelo / texto azul = valores que você pode editar.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H200"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="52.83203125" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Item</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Valor</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Observação</v>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Tamanho</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Preço</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Preço antigo</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Selo</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>WhatsApp</v>
-      </c>
-      <c r="B2" t="str">
-        <v>5581999180003</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Só números, com 55 + DDD</v>
-      </c>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Detergente Neutro</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Taxa de entrega</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Detergente Limão</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Desengordurante Cozinha</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Lava-roupas Líquido</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>3 L</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Amaciante Brisa</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>2 L</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Sabão em Barra (5 un.)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>5 × 200 g</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Água Sanitária</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Desinfecção</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>2 L</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mais vendido</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Desinfetante Lavanda</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Desinfecção</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>2 L</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Desinfetante Eucalipto 5 L</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Desinfecção</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>5 L</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Empresas</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Álcool 70% Líquido</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Desinfecção</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Limpador Multiuso</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Pisos e banheiro</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Limpa Pisos Floral</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Pisos e banheiro</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Cloro Gel Banheiro</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Pisos e banheiro</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Limpa Vidros</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Pisos e banheiro</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Esponja Dupla Face (4 un.)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Utensílios</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>4 unidades</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Pano de Chão Alvejado</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Utensílios</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Luva Látex Média</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Utensílios</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>1 par</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Kit Faxina Completa</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Kits</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>8 itens</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="8" t="n"/>
+      <c r="F65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="8" t="n"/>
+      <c r="F87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="8" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="8" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="8" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="8" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="8" t="n"/>
+      <c r="F102" s="8" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="8" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="8" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="8" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="8" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="8" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="8" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="8" t="n"/>
+      <c r="F113" s="8" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="8" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="8" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="8" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="8" t="n"/>
+      <c r="F120" s="8" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="8" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="8" t="n"/>
+      <c r="F123" s="8" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="8" t="n"/>
+      <c r="F124" s="8" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="8" t="n"/>
+      <c r="F127" s="8" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="8" t="n"/>
+      <c r="F128" s="8" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="8" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="8" t="n"/>
+      <c r="F132" s="8" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="8" t="n"/>
+      <c r="F133" s="8" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="8" t="n"/>
+      <c r="F134" s="8" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="8" t="n"/>
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="8" t="n"/>
+      <c r="F136" s="8" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="8" t="n"/>
+      <c r="F137" s="8" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="8" t="n"/>
+      <c r="F138" s="8" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="8" t="n"/>
+      <c r="F139" s="8" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="8" t="n"/>
+      <c r="F140" s="8" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="8" t="n"/>
+      <c r="F141" s="8" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="8" t="n"/>
+      <c r="F142" s="8" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="8" t="n"/>
+      <c r="F143" s="8" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="8" t="n"/>
+      <c r="F144" s="8" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="8" t="n"/>
+      <c r="F145" s="8" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="8" t="n"/>
+      <c r="F146" s="8" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="8" t="n"/>
+      <c r="F147" s="8" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="8" t="n"/>
+      <c r="F148" s="8" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="8" t="n"/>
+      <c r="F149" s="8" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="8" t="n"/>
+      <c r="F150" s="8" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="8" t="n"/>
+      <c r="F151" s="8" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="8" t="n"/>
+      <c r="F152" s="8" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="8" t="n"/>
+      <c r="F153" s="8" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="8" t="n"/>
+      <c r="F154" s="8" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="8" t="n"/>
+      <c r="F155" s="8" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="8" t="n"/>
+      <c r="F156" s="8" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="8" t="n"/>
+      <c r="F157" s="8" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="8" t="n"/>
+      <c r="F158" s="8" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="8" t="n"/>
+      <c r="F159" s="8" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="8" t="n"/>
+      <c r="F160" s="8" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="8" t="n"/>
+      <c r="F161" s="8" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="8" t="n"/>
+      <c r="F162" s="8" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="8" t="n"/>
+      <c r="F163" s="8" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="8" t="n"/>
+      <c r="F164" s="8" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="8" t="n"/>
+      <c r="F165" s="8" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="8" t="n"/>
+      <c r="F166" s="8" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="8" t="n"/>
+      <c r="F167" s="8" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="8" t="n"/>
+      <c r="F168" s="8" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="8" t="n"/>
+      <c r="F169" s="8" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="8" t="n"/>
+      <c r="F170" s="8" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="8" t="n"/>
+      <c r="F171" s="8" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="8" t="n"/>
+      <c r="F172" s="8" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="8" t="n"/>
+      <c r="F173" s="8" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="8" t="n"/>
+      <c r="F174" s="8" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="8" t="n"/>
+      <c r="F175" s="8" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="8" t="n"/>
+      <c r="F176" s="8" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="8" t="n"/>
+      <c r="F177" s="8" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="8" t="n"/>
+      <c r="F178" s="8" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="8" t="n"/>
+      <c r="F179" s="8" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="8" t="n"/>
+      <c r="F180" s="8" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="8" t="n"/>
+      <c r="F181" s="8" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="8" t="n"/>
+      <c r="F182" s="8" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="8" t="n"/>
+      <c r="F183" s="8" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="8" t="n"/>
+      <c r="F184" s="8" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="8" t="n"/>
+      <c r="F185" s="8" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="8" t="n"/>
+      <c r="F186" s="8" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="8" t="n"/>
+      <c r="F187" s="8" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="8" t="n"/>
+      <c r="F188" s="8" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="8" t="n"/>
+      <c r="F189" s="8" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="8" t="n"/>
+      <c r="F190" s="8" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="8" t="n"/>
+      <c r="F191" s="8" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="8" t="n"/>
+      <c r="F192" s="8" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="8" t="n"/>
+      <c r="F193" s="8" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="8" t="n"/>
+      <c r="F194" s="8" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="8" t="n"/>
+      <c r="F195" s="8" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="8" t="n"/>
+      <c r="F196" s="8" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="8" t="n"/>
+      <c r="F197" s="8" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="8" t="n"/>
+      <c r="F198" s="8" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="8" t="n"/>
+      <c r="F199" s="8" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="8" t="n"/>
+      <c r="F200" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Cozinha,Roupas,Pisos e banheiro,Desinfecção,Utensílios,Kits"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>5581999180003</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Só números, com 55 + DDD. Ex.: 5581988887777</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Taxa de entrega</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C3" t="str">
-        <v>Valor cobrado quando o pedido não tem frete grátis</v>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Valor cobrado quando o pedido não tem frete grátis</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Frete grátis a partir de</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Frete grátis a partir de</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="C4" t="str">
-        <v>Pedidos a partir deste valor não pagam entrega</v>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Pedidos a partir deste valor não pagam entrega</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Endereço</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Avenida B nº 5 Loja C, Maranguape II, Paulista-PE, CEP,:53.421-036</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Aparece na seção Contato do site</v>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Endereço</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Avenida B, nº 5, Loja C – Maranguape II, Paulista – PE, CEP 53421-036</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Aparece na seção Contato do site</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -33,9 +33,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="&quot;R$&quot; #,##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -66,9 +65,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -438,35 +436,9 @@
         <v>Foto</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Sim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Inseticida Poderoso</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>500</v>
-      </c>
-      <c r="E2" s="1">
-        <v>16.49</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>inseticida-poderoso-mv5g0p56.jpg</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -496,7 +468,7 @@
         <v>WhatsApp</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>5581999180003</v>
       </c>
       <c r="C2" t="str">
         <v>Só números, com 55 + DDD</v>
@@ -529,7 +501,7 @@
         <v>Endereço</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Avenida B nº 5 Loja C, Maranguape II, Paulista-PE, CEP,:53.421-036</v>
       </c>
       <c r="C5" t="str">
         <v>Aparece na seção Contato do site</v>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -1,56 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Produtos" sheetId="1" r:id="rId1"/>
-    <sheet name="Configurações" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configurações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001747D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,14 +62,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -151,7 +219,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -186,7 +253,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -221,16 +287,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,164 +422,841 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Ativo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Categoria</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Tamanho</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Preço</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Preço antigo</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Selo</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Foto</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tamanho</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Preço</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Preço antigo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Selo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Inseticida Poderoso</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Inseticidas</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>inseticida-poderoso-mv5g0p56.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido L'oeil Tutti Frutti</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-l-oeil-tutti-frutti.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido L'oeil Beijo Doce</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-l-oeil-beijo-doce.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido L'oeil Banana Pop</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-l-oeil-banana-pop.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido L'oeil Morango</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-l-oeil-morango.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido Kapelli Aloe Vera</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-kapelli-aloe-vera.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido Nathy Lavanda</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-nathy-lavanda.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido Nathy Erva Doce</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-nathy-erva-doce.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido Nathy Frescor Marinho</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-nathy-frescor-marinho.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete Líquido Nathy Flor de Cerejeira</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Sabonetes líquidos</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>sabonete-liquido-nathy-flor-de-cerejeira.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Evita Mofo Leve Brisa Lavanda</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Antimofo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>80 g</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>evita-mofo-leve-brisa-lavanda.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Evita Mofo Leve Brisa Erva Doce</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Antimofo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>80 g</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>evita-mofo-leve-brisa-erva-doce.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Evita Mofo Leve Brisa Neutro</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Antimofo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80 g</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>evita-mofo-leve-brisa-neutro.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Odorizador de Tecidos Rainha da Limpeza Downe</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="3" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>odorizador-de-tecidos-rainha-da-limpeza-downe.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Óleo de Essência Rainha da Limpeza Downe</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>oleo-de-essencia-rainha-da-limpeza-downe.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Óleo de Essência Rainha da Limpeza Herbal</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>oleo-de-essencia-rainha-da-limpeza-herbal.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Óleo de Essência Rainha da Limpeza Canela e Folhas</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>oleo-de-essencia-rainha-da-limpeza-canela-e-folhas.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Óleo de Essência Rainha da Limpeza Palmolux</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>oleo-de-essencia-rainha-da-limpeza-palmolux.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Óleo de Essência Rainha da Limpeza Lavanda</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>oleo-de-essencia-rainha-da-limpeza-lavanda.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Difusor de Aromas Tropical Aromas Cravo e Canela</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>250 ml</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>difusor-de-aromas-tropical-aromas-cravo-e-canela.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Difusor de Aromas Tropical Aromas Flor de Cerejeira</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Aromatizantes</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>250 ml</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>difusor-de-aromas-tropical-aromas-flor-de-cerejeir.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="52.83203125" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Item</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Valor</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Observação</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>WhatsApp</v>
-      </c>
-      <c r="B2" t="str">
-        <v>5581999180003</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Só números, com 55 + DDD</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>5581999180003</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Só números, com 55 + DDD</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Taxa de entrega</v>
-      </c>
-      <c r="B3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Taxa de entrega</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" t="str">
-        <v>Valor cobrado quando o pedido não tem frete grátis</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Valor cobrado quando o pedido não tem frete grátis</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Frete grátis a partir de</v>
-      </c>
-      <c r="B4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Frete grátis a partir de</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>120</v>
       </c>
-      <c r="C4" t="str">
-        <v>Pedidos a partir deste valor não pagam entrega</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pedidos a partir deste valor não pagam entrega</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Endereço</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Avenida B nº 5 Loja C, Maranguape II, Paulista-PE, CEP,:53.421-036</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Aparece na seção Contato do site</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Endereço</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Avenida B, nº 5, Loja C – Maranguape II, Paulista – PE, CEP 53421-036</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Aparece na seção Contato do site</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -981,7 +981,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>difusor-de-aromas-tropical-aromas-flor-de-cerejeir.jpg</v>
+        <v>difusor-de-aromas-tropical-aromas-flor-d-mv5jw50w.jpg</v>
       </c>
     </row>
   </sheetData>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>evita-mofo-leve-brisa-erva-doce.jpg</v>
+        <v>evita-mofo-leve-brisa-erva-doce-mv5jxoj3.jpg</v>
       </c>
     </row>
     <row r="14">

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>evita-mofo-leve-brisa-neutro.jpg</v>
+        <v>evita-mofo-leve-brisa-neutro-mv5jz2ae.jpg</v>
       </c>
     </row>
     <row r="15">

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -993,7 +993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -1055,9 +1055,64 @@
         <v>Aparece na seção Contato do site</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Chave Pix</v>
+      </c>
+      <c r="B6" t="str">
+        <v>67905362000100</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Chave Pix da loja (pedidos do site e PDV)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Tipo da chave Pix</v>
+      </c>
+      <c r="B7" t="str">
+        <v>CNPJ/CPF</v>
+      </c>
+      <c r="C7" t="str">
+        <v>CNPJ/CPF, Celular, E-mail ou Chave aleatória</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Nome do favorecido Pix</v>
+      </c>
+      <c r="B8" t="str">
+        <v>POP BRILHO</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Até 25 letras</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Cidade do Pix</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PAULISTA</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Até 15 letras</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Link de pagamento</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>Link de pagamento com cartão do banco/maquininha</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -1104,7 +1104,7 @@
         <v>Link de pagamento</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>https://payment-link-v3.ton.com.br/pl_RZp2QG3XVM7DZpvsJ5tEjaW4ovKwy5Am</v>
       </c>
       <c r="C10" t="str">
         <v>Link de pagamento com cartão do banco/maquininha</v>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -1104,7 +1104,7 @@
         <v>Link de pagamento</v>
       </c>
       <c r="B10" t="str">
-        <v>https://payment-link-v3.ton.com.br/pl_RZp2QG3XVM7DZpvsJ5tEjaW4ovKwy5Am</v>
+        <v/>
       </c>
       <c r="C10" t="str">
         <v>Link de pagamento com cartão do banco/maquininha</v>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -984,9 +984,35 @@
         <v>difusor-de-aromas-tropical-aromas-flor-d-mv5jw50w.jpg</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Multi Inseticida</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Inseticidas</v>
+      </c>
+      <c r="D23" t="str">
+        <v>250 ml</v>
+      </c>
+      <c r="E23" s="1">
+        <v>10</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>multi-inseticida-mv6v1lnr.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1010,9 +1010,61 @@
         <v>multi-inseticida-mv6v1lnr.jpg</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Perfume de Ambiente - Orquidea</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Ambientes</v>
+      </c>
+      <c r="D24" t="str">
+        <v>240 ml</v>
+      </c>
+      <c r="E24" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>perfume-de-ambiente-orquidea-mv6vw10y.jpg</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Perfume de Ambiente - Bambu</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Ambientes</v>
+      </c>
+      <c r="D25" t="str">
+        <v>240 ml</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>perfume-de-ambiente-bambu-mv6vxra9.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H25"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1062,9 +1062,35 @@
         <v>perfume-de-ambiente-bambu-mv6vxra9.jpg</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Odorizador de Tecidos - Downe</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Odorizadores</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="1">
+        <v>17.99</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>odorizador-de-tecidos-downe-mv6w3zp9.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H26"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -778,19 +778,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="B15" t="str">
-        <v>Odorizador de Tecidos Rainha da Limpeza Downe</v>
+        <v>Óleo de Essência Rainha da Limpeza Downe</v>
       </c>
       <c r="C15" t="str">
         <v>Aromatizantes</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>100 ml</v>
       </c>
       <c r="E15" s="1">
-        <v>17.99</v>
+        <v>9.99</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -799,15 +799,15 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>odorizador-de-tecidos-rainha-da-limpeza-downe.jpg</v>
+        <v>oleo-de-essencia-rainha-da-limpeza-downe.jpg</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="B16" t="str">
-        <v>Óleo de Essência Rainha da Limpeza Downe</v>
+        <v>Óleo de Essência Rainha da Limpeza Herbal</v>
       </c>
       <c r="C16" t="str">
         <v>Aromatizantes</v>
@@ -825,7 +825,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>oleo-de-essencia-rainha-da-limpeza-downe.jpg</v>
+        <v>oleo-de-essencia-rainha-da-limpeza-herbal.jpg</v>
       </c>
     </row>
     <row r="17">
@@ -833,7 +833,7 @@
         <v>Sim</v>
       </c>
       <c r="B17" t="str">
-        <v>Óleo de Essência Rainha da Limpeza Herbal</v>
+        <v>Óleo de Essência Rainha da Limpeza Canela e Folhas</v>
       </c>
       <c r="C17" t="str">
         <v>Aromatizantes</v>
@@ -851,7 +851,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>oleo-de-essencia-rainha-da-limpeza-herbal.jpg</v>
+        <v>oleo-de-essencia-rainha-da-limpeza-canela-e-folhas.jpg</v>
       </c>
     </row>
     <row r="18">
@@ -859,7 +859,7 @@
         <v>Sim</v>
       </c>
       <c r="B18" t="str">
-        <v>Óleo de Essência Rainha da Limpeza Canela e Folhas</v>
+        <v>Óleo de Essência Rainha da Limpeza Palmolux</v>
       </c>
       <c r="C18" t="str">
         <v>Aromatizantes</v>
@@ -877,7 +877,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>oleo-de-essencia-rainha-da-limpeza-canela-e-folhas.jpg</v>
+        <v>oleo-de-essencia-rainha-da-limpeza-palmolux.jpg</v>
       </c>
     </row>
     <row r="19">
@@ -885,7 +885,7 @@
         <v>Sim</v>
       </c>
       <c r="B19" t="str">
-        <v>Óleo de Essência Rainha da Limpeza Palmolux</v>
+        <v>Óleo de Essência Rainha da Limpeza Lavanda</v>
       </c>
       <c r="C19" t="str">
         <v>Aromatizantes</v>
@@ -903,7 +903,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>oleo-de-essencia-rainha-da-limpeza-palmolux.jpg</v>
+        <v>oleo-de-essencia-rainha-da-limpeza-lavanda.jpg</v>
       </c>
     </row>
     <row r="20">
@@ -911,16 +911,16 @@
         <v>Sim</v>
       </c>
       <c r="B20" t="str">
-        <v>Óleo de Essência Rainha da Limpeza Lavanda</v>
+        <v>Difusor de Aromas Tropical Aromas Cravo e Canela</v>
       </c>
       <c r="C20" t="str">
         <v>Aromatizantes</v>
       </c>
       <c r="D20" t="str">
-        <v>100 ml</v>
+        <v>250 ml</v>
       </c>
       <c r="E20" s="1">
-        <v>9.99</v>
+        <v>12.13</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -929,7 +929,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>oleo-de-essencia-rainha-da-limpeza-lavanda.jpg</v>
+        <v>difusor-de-aromas-tropical-aromas-cravo--mv5jtyqt.jpg</v>
       </c>
     </row>
     <row r="21">
@@ -937,7 +937,7 @@
         <v>Sim</v>
       </c>
       <c r="B21" t="str">
-        <v>Difusor de Aromas Tropical Aromas Cravo e Canela</v>
+        <v>Difusor de Aromas Tropical Aromas Flor de Cerejeira</v>
       </c>
       <c r="C21" t="str">
         <v>Aromatizantes</v>
@@ -955,7 +955,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>difusor-de-aromas-tropical-aromas-cravo--mv5jtyqt.jpg</v>
+        <v>difusor-de-aromas-tropical-aromas-flor-d-mv5jw50w.jpg</v>
       </c>
     </row>
     <row r="22">
@@ -963,16 +963,16 @@
         <v>Sim</v>
       </c>
       <c r="B22" t="str">
-        <v>Difusor de Aromas Tropical Aromas Flor de Cerejeira</v>
+        <v>Multi Inseticida</v>
       </c>
       <c r="C22" t="str">
-        <v>Aromatizantes</v>
+        <v>Inseticidas</v>
       </c>
       <c r="D22" t="str">
         <v>250 ml</v>
       </c>
       <c r="E22" s="1">
-        <v>12.13</v>
+        <v>10</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -981,7 +981,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>difusor-de-aromas-tropical-aromas-flor-d-mv5jw50w.jpg</v>
+        <v>multi-inseticida-mv6v1lnr.jpg</v>
       </c>
     </row>
     <row r="23">
@@ -989,16 +989,16 @@
         <v>Sim</v>
       </c>
       <c r="B23" t="str">
-        <v>Multi Inseticida</v>
+        <v>Perfume de Ambiente - Orquidea</v>
       </c>
       <c r="C23" t="str">
-        <v>Inseticidas</v>
+        <v>Ambientes</v>
       </c>
       <c r="D23" t="str">
-        <v>250 ml</v>
+        <v>240 ml</v>
       </c>
       <c r="E23" s="1">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1007,7 +1007,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>multi-inseticida-mv6v1lnr.jpg</v>
+        <v>perfume-de-ambiente-orquidea-mv6vw10y.jpg</v>
       </c>
     </row>
     <row r="24">
@@ -1015,7 +1015,7 @@
         <v>Sim</v>
       </c>
       <c r="B24" t="str">
-        <v>Perfume de Ambiente - Orquidea</v>
+        <v>Perfume de Ambiente - Bambu</v>
       </c>
       <c r="C24" t="str">
         <v>Ambientes</v>
@@ -1033,7 +1033,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>perfume-de-ambiente-orquidea-mv6vw10y.jpg</v>
+        <v>perfume-de-ambiente-bambu-mv6vxra9.jpg</v>
       </c>
     </row>
     <row r="25">
@@ -1041,16 +1041,16 @@
         <v>Sim</v>
       </c>
       <c r="B25" t="str">
-        <v>Perfume de Ambiente - Bambu</v>
+        <v>Odorizador de Tecidos - Downe</v>
       </c>
       <c r="C25" t="str">
-        <v>Ambientes</v>
+        <v>Odorizadores</v>
       </c>
       <c r="D25" t="str">
-        <v>240 ml</v>
+        <v/>
       </c>
       <c r="E25" s="1">
-        <v>8.5</v>
+        <v>17.99</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -1059,38 +1059,12 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>perfume-de-ambiente-bambu-mv6vxra9.jpg</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Sim</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Odorizador de Tecidos - Downe</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Odorizadores</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" s="1">
-        <v>17.99</v>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
         <v>odorizador-de-tecidos-downe-mv6w3zp9.jpg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H25"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1062,9 +1062,35 @@
         <v>odorizador-de-tecidos-downe-mv6w3zp9.jpg</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Pano de Chão Pequeno</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Tecidos</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="1">
+        <v>5</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>pano-de-chao-pequeno-mv7ht7ax.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H26"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="E26" s="1">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="F26" t="str">
         <v/>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="B15" t="str">
         <v>Óleo de Essência Rainha da Limpeza Downe</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>oleo-de-essencia-rainha-da-limpeza-downe.jpg</v>
+        <v>oleo-de-essencia-rainha-da-limpeza-downe-mv8akgg6.jpg</v>
       </c>
     </row>
     <row r="16">
@@ -1088,9 +1088,35 @@
         <v>pano-de-chao-pequeno-mv7ht7ax.jpg</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Difusor de Aromas Morango c/Champagne</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Aromatizantes</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" s="1">
+        <v>12.13</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>difusor-de-aromas-morango-c-champagne-mv8afuru.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H27"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -833,7 +833,7 @@
         <v>Sim</v>
       </c>
       <c r="B17" t="str">
-        <v>Óleo de Essência Rainha da Limpeza Canela e Folhas</v>
+        <v>Óleo de Essência Rainha da Limpeza Casca e Folhas</v>
       </c>
       <c r="C17" t="str">
         <v>Aromatizantes</v>
@@ -1114,9 +1114,35 @@
         <v>difusor-de-aromas-morango-c-champagne-mv8afuru.jpg</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Óleo de Essência Rainha Campim Limão</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Aromatizantes</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>oleo-de-essencia-rainha-campim-limao-mv8atsg1.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H28"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H31"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1140,9 +1140,87 @@
         <v>oleo-de-essencia-rainha-campim-limao-mv8atsg1.jpg</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Pulverizador Plastico Pequeno</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Pulverizadores</v>
+      </c>
+      <c r="D29" t="str">
+        <v>680 ml</v>
+      </c>
+      <c r="E29" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>pulverizador-plastico-mvb5u6zq.jpg</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Pulverizador Plastico Grande</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Pulverizadores</v>
+      </c>
+      <c r="D30" t="str">
+        <v>1 L</v>
+      </c>
+      <c r="E30" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>pulverizador-plastico-grande-mvb5z81e.jpg</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Pulverizador Plastico - Medio</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Pulverizadores</v>
+      </c>
+      <c r="D31" t="str">
+        <v>900 ml</v>
+      </c>
+      <c r="E31" s="1">
+        <v>16.99</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>pulverizador-plastico-medio-mvb64jyg.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H34"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1218,9 +1218,87 @@
         <v>pulverizador-plastico-medio-mvb64jyg.jpg</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Odorizador de Tecidos - Cereja com Avelã</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Odorizadores</v>
+      </c>
+      <c r="D32" t="str">
+        <v>200 ml</v>
+      </c>
+      <c r="E32" s="1">
+        <v>17.99</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>odorizador-de-tecidos-cereja-com-avela-mvic7cd7.jpg</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Odorizador de Tecidos - Flor de Cerejeira</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Odorizadores</v>
+      </c>
+      <c r="D33" t="str">
+        <v>200 ml</v>
+      </c>
+      <c r="E33" s="1">
+        <v>17.99</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>odorizador-de-tecidos-flor-de-cerejeira-mvichi77.jpg</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Odorizador de Tecidos - Palmolux</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Odorizadores</v>
+      </c>
+      <c r="D34" t="str">
+        <v>200 ml</v>
+      </c>
+      <c r="E34" s="1">
+        <v>17.99</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>odorizador-de-tecidos-palmolux-mvicgd2r.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H34"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1296,9 +1296,35 @@
         <v>odorizador-de-tecidos-palmolux-mvicgd2r.jpg</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Papel Higienico 12 rolos - Familiar</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Papel Higienico</v>
+      </c>
+      <c r="D35" t="str">
+        <v>20 m x 10 cm</v>
+      </c>
+      <c r="E35" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>papel-higienico-12-rolos-familiar-mvikr1jt.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H35"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1322,9 +1322,61 @@
         <v>papel-higienico-12-rolos-familiar-mvikr1jt.jpg</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Papel Higienico 12 rolos - Usual</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Papel Higienico</v>
+      </c>
+      <c r="D36" t="str">
+        <v>20 m x 10 cm</v>
+      </c>
+      <c r="E36" s="1">
+        <v>13</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>papel-higienico-12-rolos-usual-mvikw3em.jpg</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Papel Higienico 12 rolos - Real</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Papel Higienico</v>
+      </c>
+      <c r="D37" t="str">
+        <v>10 cm x 30 m</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>papel-higienico-12-rolos-real-mvikyrid.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H37"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1374,9 +1374,35 @@
         <v>papel-higienico-12-rolos-real-mvikyrid.jpg</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Saco para Lixo Ideal Plast</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Saco de Lixo</v>
+      </c>
+      <c r="D38" t="str">
+        <v>20 L</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5.65</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H38"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1400,9 +1400,35 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Desinfetante Neo Limpe - Herbal</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Desinfetantes</v>
+      </c>
+      <c r="D39" t="str">
+        <v>5 L</v>
+      </c>
+      <c r="E39" s="1">
+        <v>12</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>desinfetante-neo-limpe-herbai-mvpov1la.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1426,9 +1426,35 @@
         <v>desinfetante-neo-limpe-herbai-mvpov1la.jpg</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Desinfetante Neo Limpe - Talco</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Desinfetantes</v>
+      </c>
+      <c r="D40" t="str">
+        <v>5 L</v>
+      </c>
+      <c r="E40" s="1">
+        <v>12</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>desinfetante-neo-limpe-talco-mvppnkbi.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H40"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1452,9 +1452,35 @@
         <v>desinfetante-neo-limpe-talco-mvppnkbi.jpg</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Desinfetante Neo Limpe - Lavanda</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Desinfetantes</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" s="1">
+        <v>12</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>desinfetante-neo-limpe-lavanda-mvppr86z.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H41"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1478,9 +1478,35 @@
         <v>desinfetante-neo-limpe-lavanda-mvppr86z.jpg</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Desinfetante Neo Limpe - Floral</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Desinfetantes</v>
+      </c>
+      <c r="D42" t="str">
+        <v>5 L</v>
+      </c>
+      <c r="E42" s="1">
+        <v>5.99</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>desinfetante-neo-limpe-floral-mvppxexs.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H42"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1504,9 +1504,35 @@
         <v>desinfetante-neo-limpe-floral-mvppxexs.jpg</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Desinfetante Lavy Max - Essencia Real</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Desinfetantes</v>
+      </c>
+      <c r="D43" t="str">
+        <v>5 L</v>
+      </c>
+      <c r="E43" s="1">
+        <v>12</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H43"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -1492,7 +1492,7 @@
         <v>5 L</v>
       </c>
       <c r="E42" s="1">
-        <v>5.99</v>
+        <v>12</v>
       </c>
       <c r="F42" t="str">
         <v/>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1530,9 +1530,35 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Desinfetante Lavy Max - Encanto Floral</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Desinfetantes</v>
+      </c>
+      <c r="D44" t="str">
+        <v>5 L</v>
+      </c>
+      <c r="E44" s="1">
+        <v>12</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>desinfetante-lavy-max-encanto-floral-mvpqcapk.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H44"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -1527,7 +1527,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>desinfetante-lavy-max-essencia-real-mvpqenji.jpg</v>
       </c>
     </row>
     <row r="44">

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1556,9 +1556,35 @@
         <v>desinfetante-lavy-max-encanto-floral-mvpqcapk.jpg</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Desinfetante Lavy Max - Brisa do Mar</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Desinfetantes</v>
+      </c>
+      <c r="D45" t="str">
+        <v>5 L</v>
+      </c>
+      <c r="E45" s="1">
+        <v>12</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>desinfetante-lavy-max-brisa-do-mar-mvpqhkzw.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H45"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1582,9 +1582,35 @@
         <v>desinfetante-lavy-max-brisa-do-mar-mvpqhkzw.jpg</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Pano de Prato</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Tecidos</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H46"/>
   </ignoredErrors>
 </worksheet>
 </file>
